--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已实现待提交</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已实现待提交</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已实现待提交</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>已实现待提交</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>AppID/AppSecret credential type、账号认证元数据</t>
+          <t>wechat-direct 凭据/档案模型、能力协商矩阵、只读能力查询</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Secret 仅在主进程加密 Store；能力由账号类型和认证状态协商</t>
+          <t>Secret 仅在主进程加密 Store；能力由账号类型、认证状态、白名单与平台权限集共同协商</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中：AppSecret 属 client secret，禁止经渲染进程输入，录入 UX 须用主进程安全通道</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Token provider、缓存、过期刷新、错误映射</t>
+          <t>stable token 客户端、单飞缓存、errcode 映射、连接与权限观察入口</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>并发刷新合并；Token 不落日志；IP 白名单错误可诊断</t>
+          <t>并发刷新合并为一次出网；Token/AppSecret 不落日志与错误信息；IP 白名单错误可诊断；接口权限只能由真实调用观察</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>中：出口 IP</t>
+          <t>中：出口 IP 待真机验证；微信不返回权限清单</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>素材上传 Adapter、内容哈希缓存</t>
+          <t>素材预检、SHA-256 复用缓存、临时/永久/内联上传、media_id 血缘</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>格式/大小预检；重复素材复用；平台 media_id 可追溯</t>
+          <t>魔数识别格式不信任扩展名；重复内容直接复用不出网；media_id 与失败尝试均可追溯；不保存本地绝对路径</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>中：平台限制</t>
+          <t>中：平台限制为本地快照，需真机核对</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>draft API Adapter</t>
+          <t>草稿增改查删、本地↔media_id 映射、平台更新比对</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>本地草稿与 media_id 映射；更新冲突和删除失败可恢复</t>
+          <t>更新前比对平台更新时间，他人修改时阻止并可强制覆盖或以平台为准；删除失败标记可重试，平台已不存在则幂等恢复</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中：平台限制为本地快照，需真机核对</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2047,17 +2047,17 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>真实执行器、单次授权、审计回执</t>
+          <t>执行器注册表、单次执行声明、结果分类、对账与重试边界、回执审计</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>未经审批不可调用 publish；同一审批最多执行一次</t>
+          <t>未批准/已拒绝/已执行都不可执行；并发只有一个取得执行权；缺执行器时保持已批准且不退回模拟；结果未知必须先对账再重试</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高：执行器随 P2-05 接入</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -1974,7 +1974,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1992,17 +1992,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>提交、查询、回调/轮询、最终状态映射</t>
+          <t>提交/查询状态机、publish_id 持久化、状态映射、提交对账、发布执行器</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>提交成功不等于发布成功；保存 publish_id；重复提交幂等</t>
+          <t>提交只代表受理，必须经 publishing 并由查询决定结果；未映射状态码一律 unknown；同草稿重复与并发提交只出网一次；提交结果未知时必须先对账</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>高：审核结果</t>
+          <t>高：审核结果为平台异步结果，需真机验证</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2194,7 +2194,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>连接向导、权限矩阵、发布状态时间线</t>
+          <t>连接向导与权限矩阵、发布回执与状态时间线、对账入口</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>用户看到主体/认证/权限缺口；失败原因和重试边界明确</t>
+          <t>待解决事项集中展示（凭据/认证/白名单/未校验）；权限矩阵逐项给出原因；未映射状态显示结果未知；失败原因与能否重试写在卡片上；AppSecret 不经渲染进程</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>低：凭据录入需主进程安全通道，尚未实现</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>用户增减、内容阅读/分享等快照同步</t>
+          <t>用户增长/累计与新旧图文统计同步、窗口校验、覆盖与延迟概览、洞察面板</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>遵守日期窗口和延迟；新旧统计接口口径分开保存</t>
+          <t>数据延迟在本地钳制查询终点并如实展示；跨度和单日限制在本地拒绝；新旧接口与增量/累计分表分聚合，不跨口径相加；同一日期重复同步按确定性 id 覆盖</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中：延迟与窗口数值为本地快照，需真机核对</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>留言拉取、分页、去重</t>
+          <t>留言拉取、自动分页、确定性 id 去重、权限门控</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>仅账号拥有留言权限时启用；来源 msg_data_id 可追溯</t>
+          <t>仅已连接且观察到留言权限的账号启用；48001 撤销权限观察并明确报错；msg_data_id/article_index/user_comment_id 全部可追溯；只读，不实现任何留言写操作</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>中：账号权限</t>
+          <t>中：账号权限与分页数值为本地快照，需真机核对</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>commercial adapter 契约与授权证明字段</t>
+          <t>商业授权证明契约（scope/白名单/供应商许可）、门控评估与断言入口</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>无 scope/白名单证明时能力保持 disabled</t>
+          <t>无证明/未核验/过期/类型不符一律 disabled 并给出原因；商业 Adapter 构造前必须通过断言，防止先写代码后补授权</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>高：商务权限</t>
+          <t>高：商务权限，证明登记依赖人工</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>asset provenance、许可记录、生成模型元数据</t>
+          <t>素材 provenance 存储、许可状态门控、AIGC 标识检查、发布执行器阻断接入</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>每个外发素材可追溯来源；缺许可禁止进入发布审批</t>
+          <t>无来源记录/许可缺失/许可未知/许可过期均阻断外发；AIGC 素材未应用标识时按平台要求阻断；阻断发生在任何平台请求之前（not_started）</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高：来源登记依赖人工或生成工具输出</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>排程、失败策略、审批队列</t>
+          <t>本地调度规则、到期触发生成审批、运行历史、失败策略、自动化面板</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>自动化只创建待审批动作；无预授权不得外发；失败不补发风暴</t>
+          <t>自动化只 import requestControlledAction（代码层面无法越权外发）；规则创建与触发都要求执行器可用；同一触发时刻幂等；离线补跑只处理最近一次不做追赶；连续 3 次失败自动停用并写审计</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中：调度循环随应用启动</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>广告法、平台规则、版权与危机升级规则</t>
+          <t>四类内置规则（广告法/平台/版权/危机）、扫描与升级人工链路、发布执行器接入</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>高风险只给修改建议并升级人工；不自动判定法律合规</t>
+          <t>守卫只给修改建议并升级人工，不做任何阻断；免责声明明确不构成法律意见；升级写入审计（含命中词与建议）；版权阻断由 P4-09 provenance 承担</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>高：规则维护</t>
+          <t>高：内置规则为常见风险信号快照，规则库需产品/法务持续维护</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>feature flag、灰度名单、回滚手册</t>
+          <t>能力 kill switch（平台/账号两级）、灰度 allowlist 阶段、恢复机制、回滚手册</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>按平台/租户关闭能力；不删除历史审计；故障可在目标时间内回滚</t>
+          <t>默认启用、命中最具体覆盖；关闭即时生效且动作保留原状态可重试；恢复不删除历史审计；回滚手册 docs/new-media-rollback-playbook.md</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中：当前为单机语义，P3 服务端落地后需增补服务端开关</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2322,17 +2322,17 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>认证、权限集、测试账号和全网发布审核</t>
+          <t>申请材料清单、权限集草案、隐私政策要点（.context/notes/wechat-open-platform-application.md）</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>平台审核通过；权限集和隐私政策与产品描述一致</t>
+          <t>平台审核通过；权限集和隐私政策与产品描述一致（材料已备齐，等待企业主体/域名/IP 白名单就绪后提交）</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>高：资质/审核</t>
+          <t>高：资质/审核，周期 2-4 周，须尽早启动；全网发布前需补消息转发能力</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>签名验证、消息解密、ticket 存储</t>
+          <t>消息加解密、签名验证、时间戳与 nonce 双重重放拒绝、AES-GCM 加密 ticket 存储、GET 验证、app.ts 路由挂载</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>拒绝伪造/重放；密钥不进日志；回调可观测</t>
+          <t>验签失败/解密失败/时间戳过期/nonce 重放一律 401/403；ticket 明文只进加密存储，日志仅含指纹；receiveId 与 AppId 双重归属校验；存储失败返回 500 触发微信重推</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高：验收第 3 点（消息转发）未实现，提交全网发布前必须补齐</t>
         </is>
       </c>
     </row>

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>集中 Token manager</t>
+          <t>WechatComponentTokenService：内存快路径 + Postgres AES-256-GCM 加密持久化、过期前 10 分钟刷新、单飞并发合并、失败回退旧 token、指标计数</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>刷新并发合并、加密持久化、多实例一致</t>
+          <t>刷新并发合并、加密持久化、多实例一致；缓存命中不重发请求；失败且旧 token 有效时回退并告警，已过期则向上抛错；日志只含指纹</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>授权页、回调、授权账号落库</t>
+          <t>授权页 URL 生成（pre_auth_code + 一次性 state）、扫码回调处理（api_query_auth）、授权账号加密落库、authorizer token 缓存刷新、取消授权恢复</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>state/nonce 校验；不收集管理员密码；取消授权可恢复</t>
+          <t>state 一次性核销（Postgres DELETE 原子/内存删除），伪造与重放拒绝；扫码走微信托管页，不收集管理员密码；unauthorized 事件标记 revoked，重新授权恢复 active；token 加密落库，日志只含指纹</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>authorizer_access_token 管理器</t>
+          <t>authorizer token 刷新（缓存+单飞+轮换，P3-04 落地）；租户隔离（state 绑定 tenantId、访问/列表按租户过滤）；撤权守卫 assertAuthorizerUsable + revokedAt</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>按租户隔离；撤权事件立即禁用能力并停止任务</t>
+          <t>按租户隔离：跨租户 getToken/list/守卫一律拒绝；撤权事件立即禁用，任务前置守卫同步拒绝并停止；token 刷新单飞、refresh_token 轮换、失败回退旧值</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2744,7 +2744,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>事件 inbox、幂等消费、dead-letter</t>
+          <t>事件 inbox（Postgres payload 加密 + dedupeKey 幂等入库）、ticket 经 inbox 消费（processed/dead 状态机）、dead-letter 人工重放（replayTicketDeadLetter）、ticket 新鲜度巡检与授权账号对账（轮询恢复丢回调的 unauthorized）</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>重复回调不重复执行；丢回调可由轮询恢复；失败可人工重放</t>
+          <t>重复回调不重复执行：nonce 防线 + inbox 内容判重双保险，跨重启同报文重发最多消费一次；丢回调可恢复：ticket 过期告警 + api_get_authorizer_list 对账把本地 active 远端已移除的账号标记 revoked；失败可人工重放：/wechat/inbox/dead 列出、/wechat/inbox/replay 重放</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2579,7 +2579,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>权限集→能力矩阵</t>
+          <t>能力映射表（funcscope id→能力）、能力矩阵生成（generateCapabilityMatrix）、互斥规则提示（WECHAT_CAPABILITY_CONFLICT_RULES）、执行守卫 assertCapability、GET /wechat/authorizers/:appId/capabilities 路由</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>未授权权限不显示、不调用；互斥权限有显著提示</t>
+          <t>未授权权限不显示（enabled=false 不下发启用）、不调用（assertCapability 抛 WechatCapabilityDeniedError）；互斥权限产出 blocking 级显著提示文案；权限集 id 映射已在代码标注接入前需对照官方文档核验</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>tenant boundary 与访问控制测试</t>
+          <t>租户边界测试套件（tenant-isolation.test.ts 7 用例）+ 静默换绑防线 + Postgres list(tenantId) 过滤</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>跨租户 ID、Token、回调和报表均不可访问</t>
+          <t>跨租户 ID（list/矩阵/getToken/守卫全拒）、Token（接口输出零明文，断言字段集精确）、回调（state 绑定租户，泄露的 state 无法换绑归属）、报表（脱敏摘要）均不可访问；修复 save() 漏传 funcScopes/tenantId/revokedAt 的真实缺陷</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">

--- a/.context/plan/new-media-p0-p4-task-ledger.xlsx
+++ b/.context/plan/new-media-p0-p4-task-ledger.xlsx
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>待开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>迁移向导和数据绑定规则</t>
+          <t>迁移绑定服务（migration-service）：pending→completed→rolled_back/superseded 状态机、createMigration 规则校验、canDeleteLegacySecret 安全删除信号、Postgres proma_wechat_direct_migration 表；向导 UI 为 Electron 后续（服务端规则层已就绪）</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>历史草稿/指标保留；旧 Secret 可安全删除；不可静默换绑</t>
+          <t>历史草稿/指标保留：迁移全程零数据移动（测试断言授权账号记录不变），绑定只是元数据；旧 Secret 可安全删除：仅 completed 且平台 token 实际可取才返回 true，撤权即失效；不可静默换绑：同一 authorizer 同时只允许一条 active 绑定，重复迁移必须 changeReason 且旧记录 superseded 保留审计</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
